--- a/MPC_SPI/pomiary_SPI_AVR.xlsx
+++ b/MPC_SPI/pomiary_SPI_AVR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafal\Desktop\studia II st\praca magisterska\MPC_SPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FD56E8-6988-4D29-8D33-563C1F49AB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821B87B5-9549-465B-A3CA-BEBC1AF20A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4815" yWindow="2130" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="11">
   <si>
     <t>CS - pomaranczowy</t>
   </si>
@@ -393,7 +393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:I22"/>
+  <dimension ref="C3:I37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="19" customWidth="1"/>
@@ -540,6 +540,116 @@
     <row r="22" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D22" s="1"/>
     </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C27" s="2">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C28" s="2">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
+        <v>4000000</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C29" s="2">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3">
+        <v>8000000</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C33" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C35" s="2">
+        <v>10</v>
+      </c>
+      <c r="D35" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C36" s="2">
+        <v>10</v>
+      </c>
+      <c r="D36" s="3">
+        <v>4000000</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C37" s="2">
+        <v>10</v>
+      </c>
+      <c r="D37" s="3">
+        <v>8000000</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
